--- a/naver-place-crawler/results_nail/군위군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/군위군_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
+          <t>홍샵네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>j_beauty_9630@naver.com</t>
+          <t>beamingfall@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1457-9630</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로33길 6-15 1층</t>
+          <t>경상북도 구미시 인동32길 14-5 천년나무 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HnwCX</t>
+          <t>https://www.instagram.com/_hongshop_nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1564361941</t>
+          <t>1317894140</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564361941</t>
+          <t>https://m.place.naver.com/place/1317894140</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,34 +654,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뷰티첼리</t>
+          <t>노티드네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wlsl604@naver.com</t>
+          <t>rkdekqls005@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1356-0944</t>
+          <t>0507-1312-7543</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 22 타워밸리 1동 2층 201호, 202호</t>
+          <t>경상북도 칠곡군 석적읍 북중리11길 10 1층 103호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautycelli_nail/</t>
+          <t>https://www.instagram.com/noted_nail</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>704</v>
+        <v>192</v>
       </c>
       <c r="Q3" t="n">
-        <v>705</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1409</v>
+        <v>197</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>31143856</t>
+          <t>1529823333</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31143856</t>
+          <t>https://m.place.naver.com/place/1529823333</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -752,21 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디오르 네일</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>네일톡</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>youming100@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1360-5595</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동20길 27-36 1층 디오르네일</t>
+          <t>경상북도 구미시 산호대로35길 17</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/DIORENAIL</t>
+          <t>https://www.instagram.com/nailtalk_jo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>257</v>
       </c>
       <c r="R4" t="n">
-        <v>48</v>
+        <v>354</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1105211647</t>
+          <t>20734703</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105211647</t>
+          <t>https://m.place.naver.com/place/20734703</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,29 +842,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일 빛나</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jewell1004@naver.com</t>
+          <t>kgs3865@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1417-0501</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로10길 3-30 아트빌 1층 네일빛나</t>
+          <t>경상북도 구미시 산동읍 신당4로 68-10 근린생활시설2동 1층 111호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.bitna</t>
+          <t>https://blog.naver.com/kgs3865</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>354</v>
       </c>
       <c r="R5" t="n">
-        <v>17</v>
+        <v>358</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1324129585</t>
+          <t>1993281929</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324129585</t>
+          <t>https://m.place.naver.com/place/1993281929</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,25 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>네일, 바다</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kgs3865@naver.com</t>
+          <t>kongdw@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1486-0705</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당4로 68-10 근린생활시설2동 1층 111호</t>
+          <t>대구광역시 군위군 군위읍 중앙길 66 1층 네일바다</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kgs3865</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -960,12 +964,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -976,22 +980,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1000,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1993281929</t>
+          <t>1466734565</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993281929</t>
+          <t>https://m.place.naver.com/place/1466734565</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1022,29 +1026,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>콩네일</t>
+          <t>네일 클로버</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lucia_1010@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1395-8082</t>
+          <t>0507-1340-2851</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경상북도 구미시 흥안로3길 11 1층</t>
+          <t>경상북도 구미시 인동36길 50 코리안빌 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cong_nail.jining1?igsh=MXJ6YXd4dXd0NGxybg==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1054,7 +1058,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1075,17 +1079,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2072633283</t>
+          <t>2042045182</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072633283</t>
+          <t>https://m.place.naver.com/place/2042045182</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1116,21 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일공간</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>단아뷰티 네일바이진 산동점</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>room11st@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1344-7102</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로1길 2-1 1층 NAIL공간</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 3층 305호 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.gonggan_</t>
+          <t>https://blog.naver.com/room11st</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1145,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1165,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>127</v>
+        <v>298</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="R8" t="n">
-        <v>141</v>
+        <v>354</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1180,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1284979937</t>
+          <t>1224247985</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284979937</t>
+          <t>https://m.place.naver.com/place/1224247985</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1202,34 +1214,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>바름</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dud1tod22@naver.com</t>
+          <t>barumit@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1323-9839</t>
+          <t>0507-1453-1263</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 서중리6길 38</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 3 1동 1층 108호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://instagram.com/_kkomkkom_nail</t>
+          <t>https://open.kakao.com/o/s3EZN3Gd</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1250,7 +1262,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1259,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>474</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R9" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1274,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36630885</t>
+          <t>1083659063</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36630885</t>
+          <t>https://m.place.naver.com/place/1083659063</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1296,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일룸</t>
+          <t>뷰티좋은날 구미점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gumi_nailroom@naver.com</t>
+          <t>miffyand85@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1415-4865</t>
+          <t>0507-1329-8422</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 14 메가박스 4층</t>
+          <t>경상북도 구미시 진평7길 29 뷰티좋은날</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gumi_nailroom</t>
+          <t>https://www.instagram.com/a_good_day_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1333,7 +1345,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1353,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>128</v>
+        <v>1082</v>
       </c>
       <c r="Q10" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="R10" t="n">
-        <v>140</v>
+        <v>1126</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>120181172</t>
+          <t>1358401448</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/120181172</t>
+          <t>https://m.place.naver.com/place/1358401448</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>신쓰네일</t>
+          <t>네일픽</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>llooll1001@naver.com</t>
+          <t>onobomo84@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1389-5027</t>
+          <t>0507-1335-4721</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 15-7 구평동종합프라자 C동 1층 115호</t>
+          <t>경상북도 구미시 여헌로 74 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sins_nail_</t>
+          <t>https://blog.naver.com/onobomo84</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1427,7 +1439,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1447,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="R11" t="n">
-        <v>308</v>
+        <v>416</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1832929393</t>
+          <t>1338455310</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832929393</t>
+          <t>https://m.place.naver.com/place/1338455310</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1484,25 +1496,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>손톱모양</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>레푸스 구미산동점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>onyoubang@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1468-8014</t>
+          <t>0507-1442-4774</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로 58 다드림 5층 손톱모양</t>
+          <t>경상북도 구미시 산동읍 신당1로1길 17-7 2층 208호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_moyang/</t>
+          <t>http://instagram.com/refuss_sandong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1537,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1552,17 +1568,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1534082815</t>
+          <t>1150432914</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534082815</t>
+          <t>https://m.place.naver.com/place/1150432914</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1574,30 +1590,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>벨네일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>타다</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>car1023car@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1375-2916</t>
+          <t>0507-1301-9147</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 38-10 1층</t>
+          <t>경상북도 구미시 옥계북로 59 상가동 1층 101호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947942533/home?entry=pll</t>
+          <t>https://www.instagram.com/nail_ta_da_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1607,7 +1627,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1618,7 +1638,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1627,13 +1647,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>128</v>
+        <v>289</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="R13" t="n">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1642,17 +1662,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1214410327</t>
+          <t>1174670939</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214410327</t>
+          <t>https://m.place.naver.com/place/1174670939</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1664,34 +1684,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
+          <t>벨네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mydbfla33@naver.com</t>
+          <t>aa8852@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1415-9446</t>
+          <t>0507-1375-2916</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로25길 41 상가동 1층 104호</t>
+          <t>경상북도 구미시 여헌로 38-10 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://instagram.com/_somsomnail</t>
+          <t>https://m.place.naver.com/place/1947942533/home?entry=pll</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1701,7 +1721,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1712,7 +1732,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1721,13 +1741,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="Q14" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1736,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1521055352</t>
+          <t>1214410327</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1521055352</t>
+          <t>https://m.place.naver.com/place/1214410327</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1758,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일우디</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>dud1tod22@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1303-5277</t>
+          <t>0507-1323-9839</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 동서6길 28-14 2층 202호</t>
+          <t>경상북도 칠곡군 석적읍 서중리6길 38</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailwoody_</t>
+          <t>http://instagram.com/_kkomkkom_nail</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,13 +1835,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>474</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="R15" t="n">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1830,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1969430230</t>
+          <t>36630885</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969430230</t>
+          <t>https://m.place.naver.com/place/36630885</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAND</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>신쓰네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>llooll1001@naver.com</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1414-2054</t>
+          <t>0507-1389-5027</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5길 35 1층</t>
+          <t>경상북도 구미시 인동38길 15-7 구평동종합프라자 C동 1층 115호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3iH4qCh</t>
+          <t>https://www.instagram.com/sins_nail_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1896,7 +1920,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1905,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>95</v>
+        <v>299</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="R16" t="n">
-        <v>127</v>
+        <v>308</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1920,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1782781735</t>
+          <t>1832929393</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782781735</t>
+          <t>https://m.place.naver.com/place/1832929393</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1942,25 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>도디네일</t>
+          <t>섬섬네일 석적본점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bbuijini2@naver.com</t>
+          <t>alsl1004alsl@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1356-4712</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동28길 57-7 그리네빌 1층</t>
+          <t>경상북도 칠곡군 석적읍 서중리6길 44 1층 102호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dodi._.nail</t>
+          <t>https://www.instagram.com/somseom._.nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1995,13 +2023,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2010,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1754437228</t>
+          <t>1767641632</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754437228</t>
+          <t>https://m.place.naver.com/place/1767641632</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2032,29 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>레푸스 구미산동점</t>
+          <t>네일리 당신이 행복해지는 공간</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>onyoubang@naver.com</t>
+          <t>love2sun486@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1442-4774</t>
+          <t>0507-1302-8151</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로1길 17-7 2층 208호</t>
+          <t>경상북도 구미시 인동38길 15-14 101호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/refuss_sandong</t>
+          <t>https://instagram.com/nailee_gumi?utm_source=ig_profile_share&amp;igshid=1hfrq3xi83ko9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2089,13 +2117,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2104,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1150432914</t>
+          <t>1919352609</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150432914</t>
+          <t>https://m.place.naver.com/place/1919352609</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2126,29 +2154,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>태닝하우스</t>
+          <t>오랑쥬네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>skan564@naver.com</t>
+          <t>naribaba@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>070-8100-6614</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로3길 18-1 3층</t>
+          <t>경상북도 구미시 인동36길 17 보람빌딩 5층 라지공유오피스 6호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skan564</t>
+          <t>https://www.instagram.com/org_nail</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2163,7 +2187,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2183,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="Q19" t="n">
-        <v>279</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>303</v>
+        <v>67</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2198,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36615392</t>
+          <t>2094064094</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615392</t>
+          <t>https://m.place.naver.com/place/2094064094</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2220,29 +2244,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>마리네일</t>
+          <t>네일그리다</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hydestocker@naver.com</t>
+          <t>nailgreeda_@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1417-1570</t>
+          <t>0507-1344-0601</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동북길 175 1층</t>
+          <t>경상북도 구미시 옥계신당로5안길 14-2 103호 네일그리다</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/marinail__gumi__</t>
+          <t>https://www.instagram.com/__nailgreeda</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2277,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47</v>
+        <v>278</v>
       </c>
       <c r="Q20" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>145</v>
+        <v>291</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2292,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>178032643</t>
+          <t>1562146864</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/178032643</t>
+          <t>https://m.place.naver.com/place/1562146864</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2314,34 +2338,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>켈러네일</t>
+          <t>네일도화</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pgr8520@naver.com</t>
+          <t>khyun1029@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>054-472-3512</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로1길 7 골드클래스 상가 2층</t>
+          <t>경상북도 구미시 인동30길 23 1층 네일도화</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/keller_nail</t>
+          <t>http://pf.kakao.com/_sIxkjxj</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2362,7 +2382,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2371,13 +2391,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>327</v>
+        <v>53</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2386,17 +2406,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1996094770</t>
+          <t>1935081528</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996094770</t>
+          <t>https://m.place.naver.com/place/1935081528</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2408,25 +2428,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일가연</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>남자다운네일 구평점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dbs0896@naver.com</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1347-7918</t>
+          <t>054-471-7396</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동15길 5 섬계빌딩 1층</t>
+          <t>경상북도 구미시 인동38길 15-6 금강빌딩 103호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgayeon</t>
+          <t>https://blog.naver.com/dbs0896</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2441,7 +2465,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2452,7 +2476,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2461,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>258</v>
+        <v>19</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R22" t="n">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2476,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1868192073</t>
+          <t>34362850</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868192073</t>
+          <t>https://m.place.naver.com/place/34362850</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2498,29 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>홈네일</t>
+          <t>네일룸</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>homenail_@naver.com</t>
+          <t>gumi_nailroom@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>054-471-7708</t>
+          <t>0507-1415-4865</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동26길 54-1 1층</t>
+          <t>경상북도 구미시 인동가산로 14 메가박스 4층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/homenail_</t>
+          <t>https://blog.naver.com/gumi_nailroom</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2555,13 +2579,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R23" t="n">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2570,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>627597210</t>
+          <t>120181172</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/627597210</t>
+          <t>https://m.place.naver.com/place/120181172</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2592,29 +2616,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>문또네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>dmsrod91@naver.com</t>
-        </is>
-      </c>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1411-4460</t>
+          <t>0507-1415-9446</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로1길 21-33 1층 문또네일</t>
+          <t>경상북도 구미시 산호대로25길 41 상가동 1층 104호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moontto_nail/</t>
+          <t>http://instagram.com/_somsomnail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2649,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="R24" t="n">
-        <v>253</v>
+        <v>130</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2664,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1529598857</t>
+          <t>1521055352</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529598857</t>
+          <t>https://m.place.naver.com/place/1521055352</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2686,29 +2706,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>단아뷰티 네일바이진 산동점</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>room11st@naver.com</t>
-        </is>
-      </c>
+          <t>코멜리 뷰티</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1344-7102</t>
+          <t>0507-1355-3514</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 3층 305호 A</t>
+          <t>경상북도 구미시 인동중앙로6길 10 102호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/room11st</t>
+          <t>https://colavo.link/puxmox</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2723,7 +2739,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2743,13 +2759,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>298</v>
+        <v>141</v>
       </c>
       <c r="Q25" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>354</v>
+        <v>157</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2758,17 +2774,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1224247985</t>
+          <t>1843298280</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224247985</t>
+          <t>https://m.place.naver.com/place/1843298280</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2780,29 +2796,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>섬섬네일 석적본점</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>alsl1004alsl@naver.com</t>
-        </is>
-      </c>
+          <t>네일있지</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1356-4712</t>
+          <t>0507-1391-1297</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 서중리6길 44 1층 102호</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19 6층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somseom._.nail</t>
+          <t>https://www.instagram.com/nail_itzy</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2837,13 +2849,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2852,17 +2864,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1767641632</t>
+          <t>1679291687</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767641632</t>
+          <t>https://m.place.naver.com/place/1679291687</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2874,30 +2886,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코멜리 뷰티</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>로오브 네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>uiouio_0@naver.com</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1355-3514</t>
+          <t>0507-1363-9321</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로6길 10 102호</t>
+          <t>경상북도 구미시 옥계신당로5길 25-19 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://colavo.link/puxmox</t>
+          <t>http://pf.kakao.com/_xoUglG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2918,7 +2934,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2927,13 +2943,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="R27" t="n">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2942,17 +2958,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1843298280</t>
+          <t>1760682520</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843298280</t>
+          <t>https://m.place.naver.com/place/1760682520</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2964,30 +2980,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>뷰티좋은날 구미점</t>
+          <t>네일코드</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1329-8422</t>
+          <t>0507-1479-7046</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경상북도 구미시 진평7길 29 뷰티좋은날</t>
+          <t>경상북도 구미시 산동읍 신당인덕1로1길 24 1층, 네일코드</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a_good_day_nail</t>
+          <t>http://pf.kakao.com/_xlixbin/chat</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3008,7 +3024,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3017,13 +3033,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1078</v>
+        <v>69</v>
       </c>
       <c r="Q28" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1122</v>
+        <v>73</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3032,17 +3048,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1358401448</t>
+          <t>1691163537</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358401448</t>
+          <t>https://m.place.naver.com/place/1691163537</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3054,25 +3070,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>네일 빛나</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1345-1605</t>
+          <t>0507-1417-0501</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로1길 15 골드클래스 상가</t>
+          <t>경상북도 구미시 옥계북로10길 3-30 아트빌 1층 네일빛나</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://instagram.com/_mew_nail</t>
+          <t>https://www.instagram.com/nail._.bitna</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3098,7 +3114,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3107,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3122,17 +3138,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1948081087</t>
+          <t>1324129585</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948081087</t>
+          <t>https://m.place.naver.com/place/1324129585</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3144,29 +3160,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>별처럼 빛나는</t>
+          <t>손톱모양</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bright_as_stars@naver.com</t>
+          <t>ivy1780@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1339-8609</t>
+          <t>0507-1468-8014</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동46길 37-11 1층 별처럼 빛나는</t>
+          <t>경상북도 구미시 산동읍 신당1로 58 다드림 5층 손톱모양</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/starlight.nail_</t>
+          <t>http://www.instagram.com/nail_moyang/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3201,13 +3217,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>335</v>
+        <v>10</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3216,17 +3232,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1789448790</t>
+          <t>1534082815</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789448790</t>
+          <t>https://m.place.naver.com/place/1534082815</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3238,34 +3254,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일있지</t>
+          <t>네일쏘롱이</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gold77com@naver.com</t>
+          <t>i_haebitna@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1391-1297</t>
+          <t>0507-1433-6023</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19 6층</t>
+          <t>대구광역시 군위군 군위읍 중앙3길 6-2 103호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itzy</t>
+          <t>https://open.kakao.com/o/sxWYSB4g</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3286,7 +3302,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3295,13 +3311,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3310,17 +3326,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1679291687</t>
+          <t>1455948048</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679291687</t>
+          <t>https://m.place.naver.com/place/1455948048</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3332,25 +3348,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>이연지네일</t>
+          <t>뷰티써니</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>angel1989918@naver.com</t>
+          <t>ysp933@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1328-3062</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 3</t>
+          <t>경상북도 구미시 여헌로 6 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/leeyeonjinail</t>
+          <t>https://blog.naver.com/ysp933</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3365,7 +3385,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3385,13 +3405,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>101</v>
+        <v>511</v>
       </c>
       <c r="Q32" t="n">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="R32" t="n">
-        <v>194</v>
+        <v>693</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3400,17 +3420,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>21788268</t>
+          <t>1107699555</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21788268</t>
+          <t>https://m.place.naver.com/place/1107699555</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3422,34 +3442,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>봉봉네일</t>
+          <t>켈러네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ieeei13@naver.com</t>
+          <t>pgr8520@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1357-5294</t>
+          <t>054-472-3512</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리3길 67 2층</t>
+          <t>경상북도 구미시 산동읍 신당2로1길 7 골드클래스 상가 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XEKRxb/chat</t>
+          <t>http://instagram.com/keller_nail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3470,7 +3490,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3479,13 +3499,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q33" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="R33" t="n">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3494,17 +3514,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>610087331</t>
+          <t>1996094770</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/610087331</t>
+          <t>https://m.place.naver.com/place/1996094770</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3516,29 +3536,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오로지푸스&amp;아르떼네일 구미옥계점</t>
+          <t>태닝하우스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>artenail0@naver.com</t>
+          <t>skan564@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1363-1778</t>
+          <t>070-8100-6614</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로31길 15 8층</t>
+          <t>경상북도 구미시 인동중앙로3길 18-1 3층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orosy_gumi_okgye0</t>
+          <t>https://blog.naver.com/skan564</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3553,7 +3573,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3573,13 +3593,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>1018</v>
+        <v>279</v>
       </c>
       <c r="R34" t="n">
-        <v>1066</v>
+        <v>304</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3588,17 +3608,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>37061075</t>
+          <t>36615392</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37061075</t>
+          <t>https://m.place.naver.com/place/36615392</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3610,34 +3630,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>네일픽</t>
+          <t>당신의네일 구미점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>onobomo84@naver.com</t>
+          <t>moontique0812@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1335-4721</t>
+          <t>0507-1479-3375</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 74 1층</t>
+          <t>경상북도 구미시 인동남길 114 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onobomo84</t>
+          <t>https://youtube.com/watch?v=Lo52PXzFyJ8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3647,7 +3667,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3667,13 +3687,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>342</v>
+        <v>143</v>
       </c>
       <c r="Q35" t="n">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="R35" t="n">
-        <v>417</v>
+        <v>296</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3682,17 +3702,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1338455310</t>
+          <t>1917650763</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338455310</t>
+          <t>https://m.place.naver.com/place/1917650763</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3704,26 +3724,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일도화</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>마인드민</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bbang2ya_ho@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1349-3391</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동30길 23 1층 네일도화</t>
+          <t>경상북도 구미시 산동읍 신당1로 24 2층 213호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sIxkjxj</t>
+          <t>https://www.instagram.com/mind.min__</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3753,13 +3781,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3768,17 +3796,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1935081528</t>
+          <t>1278996028</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935081528</t>
+          <t>https://m.place.naver.com/place/1278996028</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3790,29 +3818,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일 희</t>
+          <t>네일가연</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nail-hee@naver.com</t>
+          <t>shammy_1@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1304-0479</t>
+          <t>0507-1347-7918</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동15길 19 1층</t>
+          <t>경상북도 구미시 인동15길 5 섬계빌딩 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-hee</t>
+          <t>https://www.instagram.com/nailgayeon</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3827,7 +3855,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3838,7 +3866,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3847,13 +3875,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>98</v>
+        <v>258</v>
       </c>
       <c r="Q37" t="n">
-        <v>1226</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1324</v>
+        <v>261</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3862,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1616482004</t>
+          <t>1868192073</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616482004</t>
+          <t>https://m.place.naver.com/place/1868192073</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3884,29 +3912,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오월에 네일</t>
+          <t>문또네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kyj8628@naver.com</t>
+          <t>dmsrod91@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1447-3385</t>
+          <t>0507-1411-4460</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 동중리3길 17 . 1층 오월에 네일</t>
+          <t>경상북도 구미시 옥계신당로1길 21-33 1층 문또네일</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5may_nail</t>
+          <t>https://www.instagram.com/moontto_nail/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3941,13 +3969,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>133</v>
+        <v>231</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="R38" t="n">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3956,17 +3984,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1158180040</t>
+          <t>1529598857</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158180040</t>
+          <t>https://m.place.naver.com/place/1529598857</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3978,30 +4006,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>네일리유</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>HAND</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wkosin@naver.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1448-1142</t>
+          <t>0507-1414-2054</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동30길 4 1층</t>
+          <t>경상북도 구미시 옥계신당로5길 35 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naily__u</t>
+          <t>https://open.kakao.com/o/s3iH4qCh</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4022,7 +4054,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4031,13 +4063,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="R39" t="n">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4046,17 +4078,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1604028285</t>
+          <t>1782781735</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604028285</t>
+          <t>https://m.place.naver.com/place/1782781735</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4068,29 +4100,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일바이진</t>
+          <t>홈네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>room11st@naver.com</t>
+          <t>homenail_@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1362-8102</t>
+          <t>054-471-7708</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 9-4 구평종합프라자 D동 1층 108호</t>
+          <t>경상북도 구미시 인동26길 54-1 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail__by__jin</t>
+          <t>https://blog.naver.com/homenail_</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4105,7 +4137,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4125,13 +4157,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>647</v>
+        <v>17</v>
       </c>
       <c r="Q40" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>735</v>
+        <v>17</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4140,17 +4172,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>252521148</t>
+          <t>627597210</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/252521148</t>
+          <t>https://m.place.naver.com/place/627597210</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4162,29 +4194,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>뷰티써니</t>
+          <t>네일,지야</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ysp933@naver.com</t>
+          <t>kinshalouis@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1328-3062</t>
+          <t>0507-1355-4306</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 6 1층</t>
+          <t>경상북도 구미시 인동32길 40-1 1층 네일지야</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysp933</t>
+          <t>https://www.instagram.com/nail_ziya</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4199,7 +4231,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4219,13 +4251,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>511</v>
+        <v>187</v>
       </c>
       <c r="Q41" t="n">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>693</v>
+        <v>188</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4234,17 +4266,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1107699555</t>
+          <t>1337655355</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107699555</t>
+          <t>https://m.place.naver.com/place/1337655355</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4256,29 +4288,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>폭스네일</t>
+          <t>콩네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kde529@naver.com</t>
+          <t>lucia_1010@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1366-2191</t>
+          <t>0507-1395-8082</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19</t>
+          <t>경상북도 구미시 흥안로3길 11 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foxnail_85/</t>
+          <t>https://www.instagram.com/cong_nail.jining1?igsh=MXJ6YXd4dXd0NGxybg==</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4313,13 +4345,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4328,17 +4360,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1356736986</t>
+          <t>2072633283</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356736986</t>
+          <t>https://m.place.naver.com/place/2072633283</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4350,25 +4382,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일을그리다</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>네일 희</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nail-hee@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1483-1005</t>
+          <t>0507-1304-0479</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동11길 16-5 1층 네일을그리다</t>
+          <t>경상북도 구미시 인동15길 19 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.__.grida</t>
+          <t>https://blog.naver.com/nail-hee</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4383,7 +4419,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4403,13 +4439,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>1226</v>
       </c>
       <c r="R43" t="n">
-        <v>169</v>
+        <v>1324</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4418,17 +4454,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1194330297</t>
+          <t>1616482004</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194330297</t>
+          <t>https://m.place.naver.com/place/1616482004</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4558,7 @@
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4534,29 +4570,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일온니</t>
+          <t>뷰티라움</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sunmoons2@naver.com</t>
+          <t>raum_chaeun@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1428-0388</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 14 2층 지엘뷰티(네일온니)</t>
+          <t>경상북도 칠곡군 석적읍 유학로 20 나동 6호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sunmoons2</t>
+          <t>https://blog.naver.com/raum_chaeun</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4591,13 +4623,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="R45" t="n">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4606,17 +4638,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1605125306</t>
+          <t>1433414344</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1605125306</t>
+          <t>https://m.place.naver.com/place/1433414344</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4628,25 +4660,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>노티드네일</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>네일온니</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sunmoons2@naver.com</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1312-7543</t>
+          <t>0507-1428-0388</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리11길 10 1층 103호</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 14 2층 지엘뷰티(네일온니)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noted_nail</t>
+          <t>https://blog.naver.com/sunmoons2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4661,7 +4697,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4681,13 +4717,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="R46" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4696,17 +4732,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1529823333</t>
+          <t>1605125306</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529823333</t>
+          <t>https://m.place.naver.com/place/1605125306</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4718,21 +4754,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>홍샵네일</t>
+          <t>오월에 네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1447-3385</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동32길 14-5 천년나무 1층</t>
+          <t>경상북도 칠곡군 석적읍 동중리3길 17 . 1층 오월에 네일</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_hongshop_nail</t>
+          <t>https://www.instagram.com/5may_nail</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4758,7 +4798,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4767,13 +4807,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4782,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1317894140</t>
+          <t>1158180040</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1317894140</t>
+          <t>https://m.place.naver.com/place/1158180040</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4804,29 +4844,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>그라운드네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ground_nail@naver.com</t>
-        </is>
-      </c>
+          <t>델라네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1471-4202</t>
+          <t>0507-1376-1778</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤2차 3층 301호</t>
+          <t>경상북도 구미시 산호대로35길 18 1층 델라네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ground__nail/</t>
+          <t>http://instagram.com/della_nail_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4861,13 +4897,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="R48" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4876,17 +4912,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1553063446</t>
+          <t>1036788315</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1553063446</t>
+          <t>https://m.place.naver.com/place/1036788315</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4898,21 +4934,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ahoi Room[아효이룸]</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>봉봉네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ieeei13@naver.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1357-5294</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로5길 16-11 1층 ahoi room 아효이룸</t>
+          <t>경상북도 칠곡군 석적읍 북중리3길 67 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeABmn</t>
+          <t>http://pf.kakao.com/_XEKRxb/chat</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4947,13 +4991,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>407</v>
+        <v>283</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="R49" t="n">
-        <v>413</v>
+        <v>350</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -4962,17 +5006,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>37322848</t>
+          <t>610087331</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37322848</t>
+          <t>https://m.place.naver.com/place/610087331</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4984,29 +5028,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>마담제이</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>phj5208@naver.com</t>
-        </is>
-      </c>
+          <t>이연지네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1321-3562</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 동중리8길 24 프라하 상가1층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 3</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/madam_j___</t>
+          <t>http://www.instagram.com/leeyeonjinail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5032,7 +5068,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5041,13 +5077,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="Q50" t="n">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="R50" t="n">
-        <v>96</v>
+        <v>195</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5056,17 +5092,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1883114690</t>
+          <t>21788268</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1883114690</t>
+          <t>https://m.place.naver.com/place/21788268</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5078,34 +5114,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>네일쏘롱이</t>
+          <t>제이뷰티</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>i_haebitna@naver.com</t>
+          <t>j_beauty_9630@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1433-6023</t>
+          <t>0507-1457-9630</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙3길 6-2 103호</t>
+          <t>경상북도 구미시 산호대로33길 6-15 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sxWYSB4g</t>
+          <t>http://pf.kakao.com/_HnwCX</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5135,13 +5171,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R51" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5150,17 +5186,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1455948048</t>
+          <t>1564361941</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455948048</t>
+          <t>https://m.place.naver.com/place/1564361941</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5172,29 +5208,21 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일,지야</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>kinshalouis@naver.com</t>
-        </is>
-      </c>
+          <t>디오르 네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1355-4306</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동32길 40-1 1층 네일지야</t>
+          <t>경상북도 구미시 인동20길 27-36 1층 디오르네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ziya</t>
+          <t>https://www.instagram.com/DIORENAIL</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5229,13 +5257,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>187</v>
+        <v>36</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R52" t="n">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5244,17 +5272,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1337655355</t>
+          <t>1105211647</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337655355</t>
+          <t>https://m.place.naver.com/place/1105211647</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5266,30 +5294,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일리 당신이 행복해지는 공간</t>
+          <t>별처럼 빛나는</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1302-8151</t>
+          <t>0507-1339-8609</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 15-14 101호</t>
+          <t>경상북도 구미시 인동46길 37-11 1층 별처럼 빛나는</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailee_gumi?utm_source=ig_profile_share&amp;igshid=1hfrq3xi83ko9</t>
+          <t>https://www.instagram.com/starlight.nail_</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5299,7 +5327,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5319,13 +5347,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>167</v>
+        <v>320</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>171</v>
+        <v>335</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5334,17 +5362,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1919352609</t>
+          <t>1789448790</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919352609</t>
+          <t>https://m.place.naver.com/place/1789448790</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5356,34 +5384,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>이현네일스튜디오</t>
+          <t>네일은하</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>tt68252@naver.com</t>
+          <t>lucia_1010@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0507-1477-7997</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동19길 34 1층 103호</t>
+          <t>경상북도 구미시 여헌로7길 39-1 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leehyun_studio</t>
+          <t>http://pf.kakao.com/_xgFMxiG</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5404,7 +5428,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5413,13 +5437,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>299</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>317</v>
+        <v>10</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5428,17 +5452,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1200581636</t>
+          <t>1541966803</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200581636</t>
+          <t>https://m.place.naver.com/place/1541966803</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5450,34 +5474,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>로오브 네일</t>
+          <t>네일바이진</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>uiouio_0@naver.com</t>
+          <t>room11st@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1363-9321</t>
+          <t>0507-1362-8102</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5길 25-19 1층</t>
+          <t>경상북도 구미시 인동38길 9-4 구평종합프라자 D동 1층 108호</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoUglG</t>
+          <t>http://instagram.com/nail__by__jin</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5498,7 +5522,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5507,13 +5531,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>150</v>
+        <v>648</v>
       </c>
       <c r="Q55" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="R55" t="n">
-        <v>210</v>
+        <v>736</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5522,17 +5546,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1760682520</t>
+          <t>252521148</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760682520</t>
+          <t>https://m.place.naver.com/place/252521148</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5568,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>네일은하</t>
+          <t>Ahoi Room[아효이룸]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -5553,12 +5577,12 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로7길 39-1 1층</t>
+          <t>경상북도 구미시 인동중앙로5길 16-11 1층 ahoi room 아효이룸</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xgFMxiG</t>
+          <t>http://pf.kakao.com/_xeABmn</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5593,13 +5617,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>5</v>
+        <v>407</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>413</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5608,17 +5632,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1541966803</t>
+          <t>37322848</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1541966803</t>
+          <t>https://m.place.naver.com/place/37322848</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5630,30 +5654,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>나탈리네일 스튜디오</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>뮤네일</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mieux_by_nail@naver.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1328-9155</t>
+          <t>0507-1345-1605</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 남율로9길 30 유진빌딩 1층 104호</t>
+          <t>경상북도 구미시 산동읍 신당2로1길 15 골드클래스 상가</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_BhxaUT</t>
+          <t>http://instagram.com/_mew_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5674,7 +5702,7 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5683,13 +5711,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>273</v>
+        <v>129</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>276</v>
+        <v>142</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5698,17 +5726,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1011209011</t>
+          <t>1948081087</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011209011</t>
+          <t>https://m.place.naver.com/place/1948081087</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5720,29 +5748,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일코드</t>
+          <t>네일드인</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>m__hinail@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1479-7046</t>
+          <t>0507-1364-2315</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당인덕1로1길 24 1층, 네일코드</t>
+          <t>경상북도 구미시 인동중앙로3길 6 네일드인</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlixbin/chat</t>
+          <t>https://pf.kakao.com/_xduSGG</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5777,13 +5805,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>69</v>
+        <v>1490</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>73</v>
+        <v>1493</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5792,17 +5820,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1691163537</t>
+          <t>1922958194</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691163537</t>
+          <t>https://m.place.naver.com/place/1922958194</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5814,29 +5842,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>하이비뷰티&amp;풋 본점</t>
+          <t>마리네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>tree4350@naver.com</t>
+          <t>hydestocker@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1385-7396</t>
+          <t>0507-1417-1570</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 72 하이비뷰티&amp;풋 본점</t>
+          <t>경상북도 구미시 인동북길 175 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sj_hib.beauty/</t>
+          <t>https://www.instagram.com/marinail__gumi__</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5871,13 +5899,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>345</v>
+        <v>47</v>
       </c>
       <c r="Q59" t="n">
-        <v>1138</v>
+        <v>98</v>
       </c>
       <c r="R59" t="n">
-        <v>1483</v>
+        <v>145</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5886,17 +5914,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1877586341</t>
+          <t>178032643</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877586341</t>
+          <t>https://m.place.naver.com/place/178032643</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5908,29 +5936,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일 클로버</t>
+          <t>네일공간</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>winkyster@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>0507-1340-2851</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 50 코리안빌 1층</t>
+          <t>경상북도 구미시 옥계신당로1길 2-1 1층 NAIL공간</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.gonggan_</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5940,7 +5964,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5961,17 +5985,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R60" t="n">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5980,17 +6004,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>2042045182</t>
+          <t>1284979937</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042045182</t>
+          <t>https://m.place.naver.com/place/1284979937</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6002,29 +6026,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>델라네일</t>
+          <t>손끝네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hyn9277@naver.com</t>
+          <t>pp1102qq@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1376-1778</t>
+          <t>0507-1427-6878</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로35길 18 1층 델라네일</t>
+          <t>경상북도 구미시 인동19길 27-4 다옴빌 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/della_nail_</t>
+          <t>https://blog.naver.com/pp1102qq</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6039,7 +6063,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6059,13 +6083,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R61" t="n">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6074,17 +6098,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1036788315</t>
+          <t>952100686</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036788315</t>
+          <t>https://m.place.naver.com/place/952100686</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6120,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일연구소</t>
+          <t>뷰티플럼</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jyedream@naver.com</t>
+          <t>heysoo206@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -6109,12 +6133,12 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동54안길 6-19 1층</t>
+          <t>경상북도 구미시 옥계북로 15 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/beauty__plum</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6124,7 +6148,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6145,17 +6169,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6164,17 +6188,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1916131367</t>
+          <t>1498423201</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1916131367</t>
+          <t>https://m.place.naver.com/place/1498423201</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6186,29 +6210,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일톡</t>
+          <t>하이비뷰티&amp;풋 본점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>youming100@naver.com</t>
+          <t>tree4350@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1360-5595</t>
+          <t>0507-1385-7396</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로35길 17</t>
+          <t>경상북도 칠곡군 석적읍 유학로 72 하이비뷰티&amp;풋 본점</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtalk_jo</t>
+          <t>https://www.instagram.com/sj_hib.beauty/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6243,13 +6267,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="Q63" t="n">
-        <v>257</v>
+        <v>1138</v>
       </c>
       <c r="R63" t="n">
-        <v>353</v>
+        <v>1484</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6258,17 +6282,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>20734703</t>
+          <t>1877586341</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20734703</t>
+          <t>https://m.place.naver.com/place/1877586341</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6280,25 +6304,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>뷰티플럼</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>heysoo206@naver.com</t>
-        </is>
-      </c>
+          <t>네일을그리다</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1483-1005</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 15 1층</t>
+          <t>경상북도 구미시 인동11길 16-5 1층 네일을그리다</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty__plum</t>
+          <t>https://www.instagram.com/nail.__.grida</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6333,13 +6357,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6348,17 +6372,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1498423201</t>
+          <t>1194330297</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498423201</t>
+          <t>https://m.place.naver.com/place/1194330297</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6370,25 +6394,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>바름</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>뷰티첼리</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wlsl604@naver.com</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1453-1263</t>
+          <t>0507-1356-0944</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 3 1동 1층 108호</t>
+          <t>경상북도 구미시 옥계북로 22 타워밸리 1동 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3EZN3Gd</t>
+          <t>https://www.instagram.com/beautycelli_nail/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6414,7 +6442,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6423,13 +6451,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>709</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>706</v>
       </c>
       <c r="R65" t="n">
-        <v>23</v>
+        <v>1415</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6438,17 +6466,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1083659063</t>
+          <t>31143856</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083659063</t>
+          <t>https://m.place.naver.com/place/31143856</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6460,29 +6488,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일그리다</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>nailgreeda_@naver.com</t>
-        </is>
-      </c>
+          <t>도디네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>0507-1344-0601</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5안길 14-2 103호 네일그리다</t>
+          <t>경상북도 구미시 인동28길 57-7 그리네빌 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailgreeda</t>
+          <t>https://www.instagram.com/dodi._.nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6517,13 +6537,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6532,17 +6552,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1562146864</t>
+          <t>1754437228</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562146864</t>
+          <t>https://m.place.naver.com/place/1754437228</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6554,25 +6574,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일, 바다</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>찐블링네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>hwhoskyj59@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1486-0705</t>
+          <t>0507-1321-9103</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙길 66 1층 네일바다</t>
+          <t>경상북도 구미시 인동중앙로7길 28 1층 106호 찐블링</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jjin_bling</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6582,7 +6606,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6603,17 +6627,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6622,17 +6646,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1466734565</t>
+          <t>1435433966</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1466734565</t>
+          <t>https://m.place.naver.com/place/1435433966</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6644,25 +6668,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>마인드민</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>네일리유</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>lhll0228@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1349-3391</t>
+          <t>0507-1448-1142</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로 24 2층 213호</t>
+          <t>경상북도 구미시 인동30길 4 1층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mind.min__</t>
+          <t>https://www.instagram.com/naily__u</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6688,7 +6716,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6697,13 +6725,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6712,17 +6740,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1278996028</t>
+          <t>1604028285</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278996028</t>
+          <t>https://m.place.naver.com/place/1604028285</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6734,25 +6762,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>타다</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>주주모어네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>6qbmfuw6c@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1301-9147</t>
+          <t>0507-1399-9336</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 59 상가동 1층 101호</t>
+          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤메디프라자2차 2층 202호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ta_da_</t>
+          <t>http://www.instagram.com/_juju_more</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6787,13 +6819,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>291</v>
+        <v>182</v>
       </c>
       <c r="Q69" t="n">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="R69" t="n">
-        <v>336</v>
+        <v>255</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6802,17 +6834,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1174670939</t>
+          <t>1091496299</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174670939</t>
+          <t>https://m.place.naver.com/place/1091496299</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6824,25 +6856,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>찐블링네일</t>
+          <t>네일모노</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hwhoskyj59@naver.com</t>
+          <t>ekgus9633@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1484-2855</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로7길 28 1층 106호 찐블링</t>
+          <t>경상북도 구미시 옥계신당로1길 1-15 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjin_bling</t>
+          <t>https://www.instagram.com/nail.mono_?igsh=MTQ1M2I3ajJma3M2dA==</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6877,13 +6913,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>134</v>
+        <v>4</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6892,17 +6928,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1435433966</t>
+          <t>2055274089</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435433966</t>
+          <t>https://m.place.naver.com/place/2055274089</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6914,34 +6950,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>손끝네일</t>
+          <t>나탈리네일 스튜디오</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pp1102qq@naver.com</t>
+          <t>frenchcloset@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1427-6878</t>
+          <t>0507-1328-9155</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동19길 27-4 다옴빌 1층</t>
+          <t>경상북도 칠곡군 석적읍 남율로9길 30 유진빌딩 1층 104호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pp1102qq</t>
+          <t>http://pf.kakao.com/_BhxaUT</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6951,7 +6987,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6962,7 +6998,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6971,13 +7007,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>64</v>
+        <v>273</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6986,17 +7022,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>952100686</t>
+          <t>1011209011</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/952100686</t>
+          <t>https://m.place.naver.com/place/1011209011</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7008,35 +7044,35 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일드인</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>네일연구소</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jyedream@naver.com</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1364-2315</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로3길 6 네일드인</t>
+          <t>경상북도 구미시 인동54안길 6-19 1층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xduSGG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7052,22 +7088,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1490</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>1493</v>
+        <v>4</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7076,17 +7112,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1922958194</t>
+          <t>1916131367</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922958194</t>
+          <t>https://m.place.naver.com/place/1916131367</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7098,29 +7134,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>당신의네일 구미점</t>
+          <t>오로지푸스&amp;아르떼네일 구미옥계점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>moontique0812@naver.com</t>
+          <t>artenail0@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1479-3375</t>
+          <t>0507-1363-1778</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동남길 114 1층</t>
+          <t>경상북도 구미시 산호대로31길 15 8층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Lo52PXzFyJ8</t>
+          <t>https://www.instagram.com/artenail_gumi</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7155,13 +7191,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>143</v>
+        <v>50</v>
       </c>
       <c r="Q73" t="n">
-        <v>153</v>
+        <v>1020</v>
       </c>
       <c r="R73" t="n">
-        <v>296</v>
+        <v>1070</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7170,17 +7206,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1917650763</t>
+          <t>37061075</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917650763</t>
+          <t>https://m.place.naver.com/place/37061075</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7192,25 +7228,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>오랑쥬네일</t>
+          <t>폭스네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>naribaba@naver.com</t>
+          <t>kde529@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1366-2191</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 17 보람빌딩 5층 라지공유오피스 6호</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/org_nail</t>
+          <t>https://www.instagram.com/foxnail_85/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7245,13 +7285,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>64</v>
+        <v>176</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
-        <v>66</v>
+        <v>186</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7260,17 +7300,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2094064094</t>
+          <t>1356736986</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094064094</t>
+          <t>https://m.place.naver.com/place/1356736986</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7282,29 +7322,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>주주모어네일</t>
+          <t>이현네일스튜디오</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0636535529@naver.com</t>
+          <t>tt68252@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1399-9336</t>
+          <t>0507-1477-7997</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤메디프라자2차 2층 202호</t>
+          <t>경상북도 구미시 인동19길 34 1층 103호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_juju_more</t>
+          <t>https://www.instagram.com/leehyun_studio</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7339,13 +7379,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>182</v>
+        <v>18</v>
       </c>
       <c r="Q75" t="n">
-        <v>73</v>
+        <v>300</v>
       </c>
       <c r="R75" t="n">
-        <v>255</v>
+        <v>318</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7354,17 +7394,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1091496299</t>
+          <t>1200581636</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091496299</t>
+          <t>https://m.place.naver.com/place/1200581636</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7376,25 +7416,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>뷰티라움</t>
+          <t>네일우디</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>raum_chaeun@naver.com</t>
+          <t>90heehee@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1303-5277</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 20 나동 6호</t>
+          <t>대구광역시 군위군 군위읍 동서6길 28-14 2층 202호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/raum_chaeun</t>
+          <t>http://instagram.com/nailwoody_</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7409,7 +7453,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7429,13 +7473,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7444,17 +7488,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1433414344</t>
+          <t>1969430230</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433414344</t>
+          <t>https://m.place.naver.com/place/1969430230</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/군위군_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/군위군_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>홍샵네일</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>beamingfall@naver.com</t>
+          <t>kgs3865@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -577,12 +577,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동32길 14-5 천년나무 1층</t>
+          <t>경상북도 구미시 산동읍 신당4로 68-10 근린생활시설2동 1층 111호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_hongshop_nail</t>
+          <t>https://blog.naver.com/kgs3865</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>355</v>
       </c>
       <c r="R2" t="n">
-        <v>42</v>
+        <v>359</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +632,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1317894140</t>
+          <t>1993281929</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1317894140</t>
+          <t>https://m.place.naver.com/place/1993281929</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -654,34 +654,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>노티드네일</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>rkdekqls005@naver.com</t>
-        </is>
-      </c>
+          <t>Ahoi Room[아효이룸]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1312-7543</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리11길 10 1층 103호</t>
+          <t>경상북도 구미시 인동중앙로5길 16-11 1층 ahoi room 아효이룸</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/noted_nail</t>
+          <t>http://pf.kakao.com/_xeABmn</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,7 +694,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +703,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>192</v>
+        <v>407</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>197</v>
+        <v>413</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +718,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1529823333</t>
+          <t>37322848</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529823333</t>
+          <t>https://m.place.naver.com/place/37322848</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -748,29 +740,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일톡</t>
+          <t>네일공간</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>youming100@naver.com</t>
+          <t>gol2006@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1360-5595</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로35길 17</t>
+          <t>경상북도 구미시 옥계신당로1길 2-1 1층 NAIL공간</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailtalk_jo</t>
+          <t>https://www.instagram.com/nail.gonggan_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +793,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="Q4" t="n">
-        <v>257</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>354</v>
+        <v>141</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +808,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20734703</t>
+          <t>1284979937</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20734703</t>
+          <t>https://m.place.naver.com/place/1284979937</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -842,25 +830,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>뷰티첼리</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kgs3865@naver.com</t>
+          <t>wlsl604@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1356-0944</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당4로 68-10 근린생활시설2동 1층 111호</t>
+          <t>경상북도 구미시 옥계북로 22 타워밸리 1동 2층 201호, 202호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kgs3865</t>
+          <t>https://www.instagram.com/beautycelli_nail/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -875,7 +867,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -886,7 +878,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -895,13 +887,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>712</v>
       </c>
       <c r="Q5" t="n">
-        <v>354</v>
+        <v>706</v>
       </c>
       <c r="R5" t="n">
-        <v>358</v>
+        <v>1418</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +902,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1993281929</t>
+          <t>31143856</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993281929</t>
+          <t>https://m.place.naver.com/place/31143856</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1006,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1026,29 +1018,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>네일 클로버</t>
+          <t>네일 희</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bongbong323@naver.com</t>
+          <t>nail-hee@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1340-2851</t>
+          <t>0507-1304-0479</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 50 코리안빌 1층</t>
+          <t>경상북도 구미시 인동15길 19 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail-hee</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,12 +1050,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1079,17 +1071,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>1226</v>
       </c>
       <c r="R7" t="n">
-        <v>84</v>
+        <v>1324</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1090,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2042045182</t>
+          <t>1616482004</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2042045182</t>
+          <t>https://m.place.naver.com/place/1616482004</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1112,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>단아뷰티 네일바이진 산동점</t>
+          <t>네일모노</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>room11st@naver.com</t>
+          <t>ekgus9633@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1344-7102</t>
+          <t>0507-1484-2855</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 3층 305호 A</t>
+          <t>경상북도 구미시 옥계신당로1길 1-15 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/room11st</t>
+          <t>https://www.instagram.com/nail.mono_?igsh=MTQ1M2I3ajJma3M2dA==</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1149,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1169,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>298</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>354</v>
+        <v>4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1184,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1224247985</t>
+          <t>2055274089</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224247985</t>
+          <t>https://m.place.naver.com/place/2055274089</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1206,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>바름</t>
+          <t>네일드인</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>barumit@naver.com</t>
+          <t>m__hinail@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1453-1263</t>
+          <t>0507-1364-2315</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 3 1동 1층 108호</t>
+          <t>경상북도 구미시 인동중앙로3길 6 네일드인</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3EZN3Gd</t>
+          <t>https://pf.kakao.com/_xduSGG</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1271,13 +1263,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>1491</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>23</v>
+        <v>1494</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1278,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1083659063</t>
+          <t>1922958194</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083659063</t>
+          <t>https://m.place.naver.com/place/1922958194</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1300,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뷰티좋은날 구미점</t>
+          <t>신쓰네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>miffyand85@naver.com</t>
+          <t>llooll1001@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1329-8422</t>
+          <t>0507-1389-5027</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경상북도 구미시 진평7길 29 뷰티좋은날</t>
+          <t>경상북도 구미시 인동38길 15-7 구평동종합프라자 C동 1층 115호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a_good_day_nail</t>
+          <t>https://www.instagram.com/sins_nail_</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1357,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1082</v>
+        <v>299</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>1126</v>
+        <v>308</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1372,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1358401448</t>
+          <t>1832929393</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358401448</t>
+          <t>https://m.place.naver.com/place/1832929393</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1402,34 +1394,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일픽</t>
+          <t>네일쏘롱이</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>onobomo84@naver.com</t>
+          <t>i_haebitna@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1335-4721</t>
+          <t>0507-1433-6023</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 74 1층</t>
+          <t>대구광역시 군위군 군위읍 중앙3길 6-2 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onobomo84</t>
+          <t>https://open.kakao.com/o/sxWYSB4g</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1439,7 +1431,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1450,7 +1442,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1451,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>341</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>416</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1466,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1338455310</t>
+          <t>1455948048</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1338455310</t>
+          <t>https://m.place.naver.com/place/1455948048</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1488,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레푸스 구미산동점</t>
+          <t>노티드네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>onyoubang@naver.com</t>
+          <t>rkdekqls005@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1442-4774</t>
+          <t>0507-1312-7543</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로1길 17-7 2층 208호</t>
+          <t>경상북도 칠곡군 석적읍 북중리11길 10 1층 103호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/refuss_sandong</t>
+          <t>https://www.instagram.com/noted_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1553,13 +1545,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>63</v>
+        <v>192</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1560,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1150432914</t>
+          <t>1529823333</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150432914</t>
+          <t>https://m.place.naver.com/place/1529823333</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1582,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>타다</t>
+          <t>손끝네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>car1023car@naver.com</t>
+          <t>pp1102qq@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1301-9147</t>
+          <t>0507-1427-6878</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 59 상가동 1층 101호</t>
+          <t>경상북도 구미시 인동19길 27-4 다옴빌 1층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ta_da_</t>
+          <t>https://blog.naver.com/pp1102qq</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1619,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1639,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>289</v>
+        <v>65</v>
       </c>
       <c r="Q13" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="R13" t="n">
-        <v>334</v>
+        <v>86</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1174670939</t>
+          <t>952100686</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174670939</t>
+          <t>https://m.place.naver.com/place/952100686</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,34 +1676,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>벨네일</t>
+          <t>네일우디</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>aa8852@naver.com</t>
+          <t>90heehee@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1375-2916</t>
+          <t>0507-1303-5277</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 38-10 1층</t>
+          <t>대구광역시 군위군 군위읍 동서6길 28-14 2층 202호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1947942533/home?entry=pll</t>
+          <t>http://instagram.com/nailwoody_</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1721,7 +1713,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1732,7 +1724,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1741,13 +1733,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>138</v>
+        <v>8</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1748,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1214410327</t>
+          <t>1969430230</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1214410327</t>
+          <t>https://m.place.naver.com/place/1969430230</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1770,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>꼼꼼네일</t>
+          <t>네일픽</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dud1tod22@naver.com</t>
+          <t>onobomo84@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1323-9839</t>
+          <t>0507-1335-4721</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 서중리6길 38</t>
+          <t>경상북도 구미시 여헌로 74 1층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://instagram.com/_kkomkkom_nail</t>
+          <t>https://blog.naver.com/onobomo84</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1815,7 +1807,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,13 +1827,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>474</v>
+        <v>342</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="R15" t="n">
-        <v>500</v>
+        <v>417</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36630885</t>
+          <t>1338455310</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36630885</t>
+          <t>https://m.place.naver.com/place/1338455310</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1864,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>신쓰네일</t>
+          <t>네일가연</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>llooll1001@naver.com</t>
+          <t>shammy_1@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1389-5027</t>
+          <t>0507-1347-7918</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 15-7 구평동종합프라자 C동 1층 115호</t>
+          <t>경상북도 구미시 인동15길 5 섬계빌딩 1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sins_nail_</t>
+          <t>https://www.instagram.com/nailgayeon</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1920,7 +1912,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1929,13 +1921,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>308</v>
+        <v>261</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1936,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1832929393</t>
+          <t>1868192073</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1832929393</t>
+          <t>https://m.place.naver.com/place/1868192073</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1958,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>섬섬네일 석적본점</t>
+          <t>오월에 네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>alsl1004alsl@naver.com</t>
+          <t>kyj8628@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1356-4712</t>
+          <t>0507-1447-3385</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 서중리6길 44 1층 102호</t>
+          <t>경상북도 칠곡군 석적읍 동중리3길 17 . 1층 오월에 네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/somseom._.nail</t>
+          <t>https://www.instagram.com/5may_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2023,13 +2015,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2030,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1767641632</t>
+          <t>1158180040</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767641632</t>
+          <t>https://m.place.naver.com/place/1158180040</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2060,29 +2052,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일리 당신이 행복해지는 공간</t>
+          <t>디오르 네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>love2sun486@naver.com</t>
+          <t>dodoqueen_j@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1302-8151</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 15-14 101호</t>
+          <t>경상북도 구미시 인동20길 27-36 1층 디오르네일</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://instagram.com/nailee_gumi?utm_source=ig_profile_share&amp;igshid=1hfrq3xi83ko9</t>
+          <t>https://www.instagram.com/DIORENAIL</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2117,13 +2105,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>168</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R18" t="n">
-        <v>172</v>
+        <v>48</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2120,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1919352609</t>
+          <t>1105211647</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919352609</t>
+          <t>https://m.place.naver.com/place/1105211647</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2154,25 +2142,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>오랑쥬네일</t>
+          <t>마인드민</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>naribaba@naver.com</t>
+          <t>bbang2ya_ho@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1349-3391</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 17 보람빌딩 5층 라지공유오피스 6호</t>
+          <t>경상북도 구미시 산동읍 신당1로 24 2층 213호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/org_nail</t>
+          <t>https://www.instagram.com/mind.min__</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2198,7 +2190,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2207,13 +2199,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2214,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2094064094</t>
+          <t>1278996028</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094064094</t>
+          <t>https://m.place.naver.com/place/1278996028</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2236,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일그리다</t>
+          <t>뮤네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nailgreeda_@naver.com</t>
+          <t>mieux_by_nail@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1344-0601</t>
+          <t>0507-1345-1605</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5안길 14-2 103호 네일그리다</t>
+          <t>경상북도 구미시 산동읍 신당2로1길 15 골드클래스 상가</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailgreeda</t>
+          <t>http://instagram.com/_mew_nail</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2293,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>291</v>
+        <v>142</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2308,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1562146864</t>
+          <t>1948081087</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562146864</t>
+          <t>https://m.place.naver.com/place/1948081087</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,30 +2330,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일도화</t>
+          <t>마담제이</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>khyun1029@naver.com</t>
+          <t>phj5208@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1321-3562</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동30길 23 1층 네일도화</t>
+          <t>경상북도 칠곡군 석적읍 동중리8길 24 프라하 상가1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_sIxkjxj</t>
+          <t>https://www.instagram.com/madam_j___</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2391,13 +2387,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="R21" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2402,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1935081528</t>
+          <t>1883114690</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935081528</t>
+          <t>https://m.place.naver.com/place/1883114690</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2428,29 +2424,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>남자다운네일 구평점</t>
+          <t>홈네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dbs0896@naver.com</t>
+          <t>homenail_@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>054-471-7396</t>
+          <t>054-471-7708</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 15-6 금강빌딩 103호</t>
+          <t>경상북도 구미시 인동26길 54-1 1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dbs0896</t>
+          <t>https://blog.naver.com/homenail_</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,13 +2481,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,17 +2496,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>34362850</t>
+          <t>627597210</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34362850</t>
+          <t>https://m.place.naver.com/place/627597210</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2522,29 +2518,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일룸</t>
+          <t>태닝하우스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gumi_nailroom@naver.com</t>
+          <t>skan564@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1415-4865</t>
+          <t>070-8100-6614</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 14 메가박스 4층</t>
+          <t>경상북도 구미시 인동중앙로3길 18-1 3층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gumi_nailroom</t>
+          <t>https://blog.naver.com/skan564</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2579,13 +2575,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>280</v>
       </c>
       <c r="R23" t="n">
-        <v>140</v>
+        <v>305</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2590,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>120181172</t>
+          <t>36615392</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/120181172</t>
+          <t>https://m.place.naver.com/place/36615392</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2616,25 +2612,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>솜솜네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>마리네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dbs375@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1415-9446</t>
+          <t>0507-1417-1570</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로25길 41 상가동 1층 104호</t>
+          <t>경상북도 구미시 인동북길 175 1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://instagram.com/_somsomnail</t>
+          <t>https://www.instagram.com/marinail__gumi__</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2669,13 +2669,13 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q24" t="n">
         <v>98</v>
       </c>
-      <c r="Q24" t="n">
-        <v>32</v>
-      </c>
       <c r="R24" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1521055352</t>
+          <t>178032643</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1521055352</t>
+          <t>https://m.place.naver.com/place/178032643</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>코멜리 뷰티</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>뷰티플럼</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>heysoo206@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0507-1355-3514</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로6길 10 102호</t>
+          <t>경상북도 구미시 옥계북로 15 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://colavo.link/puxmox</t>
+          <t>https://www.instagram.com/beauty__plum</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2759,14 +2759,14 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
         <v>16</v>
       </c>
-      <c r="R25" t="n">
-        <v>157</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2774,17 +2774,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1843298280</t>
+          <t>1498423201</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1843298280</t>
+          <t>https://m.place.naver.com/place/1498423201</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2796,25 +2796,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>네일있지</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>솜솜네일</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mydbfla33@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1391-1297</t>
+          <t>0507-1415-9446</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19 6층</t>
+          <t>경상북도 구미시 산호대로25길 41 상가동 1층 104호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_itzy</t>
+          <t>http://instagram.com/_somsomnail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2849,13 +2853,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="R26" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2864,17 +2868,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1679291687</t>
+          <t>1521055352</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1679291687</t>
+          <t>https://m.place.naver.com/place/1521055352</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2890,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>로오브 네일</t>
+          <t>바름</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>uiouio_0@naver.com</t>
+          <t>barumit@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1363-9321</t>
+          <t>0507-1453-1263</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5길 25-19 1층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 3 1동 1층 108호</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xoUglG</t>
+          <t>https://open.kakao.com/o/s3EZN3Gd</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2943,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="Q27" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="R27" t="n">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2958,17 +2962,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1760682520</t>
+          <t>1083659063</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760682520</t>
+          <t>https://m.place.naver.com/place/1083659063</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2980,30 +2984,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일코드</t>
+          <t>코멜리 뷰티</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1479-7046</t>
+          <t>0507-1355-3514</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당인덕1로1길 24 1층, 네일코드</t>
+          <t>경상북도 구미시 인동중앙로6길 10 102호</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlixbin/chat</t>
+          <t>https://colavo.link/puxmox</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3024,7 +3028,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3033,13 +3037,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="R28" t="n">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3048,17 +3052,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1691163537</t>
+          <t>1843298280</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1691163537</t>
+          <t>https://m.place.naver.com/place/1843298280</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3070,25 +3074,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네일 빛나</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>도디네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bbuijini2@naver.com</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1417-0501</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로10길 3-30 아트빌 1층 네일빛나</t>
+          <t>경상북도 구미시 인동28길 57-7 그리네빌 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.bitna</t>
+          <t>https://www.instagram.com/dodi._.nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3114,7 +3118,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3123,13 +3127,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3138,17 +3142,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1324129585</t>
+          <t>1754437228</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324129585</t>
+          <t>https://m.place.naver.com/place/1754437228</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3160,29 +3164,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>손톱모양</t>
+          <t>하이비뷰티&amp;풋 본점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ivy1780@naver.com</t>
+          <t>tree4350@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1468-8014</t>
+          <t>0507-1385-7396</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로 58 다드림 5층 손톱모양</t>
+          <t>경상북도 칠곡군 석적읍 유학로 72 하이비뷰티&amp;풋 본점</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_moyang/</t>
+          <t>https://www.instagram.com/sj_hib.beauty/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3217,13 +3221,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>347</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1138</v>
       </c>
       <c r="R30" t="n">
-        <v>10</v>
+        <v>1485</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3232,17 +3236,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1534082815</t>
+          <t>1877586341</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534082815</t>
+          <t>https://m.place.naver.com/place/1877586341</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3254,34 +3258,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>네일쏘롱이</t>
+          <t>네일리유</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>i_haebitna@naver.com</t>
+          <t>lhll0228@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1433-6023</t>
+          <t>0507-1448-1142</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙3길 6-2 103호</t>
+          <t>경상북도 구미시 인동30길 4 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sxWYSB4g</t>
+          <t>https://www.instagram.com/naily__u</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3302,7 +3306,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3311,13 +3315,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3326,17 +3330,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1455948048</t>
+          <t>1604028285</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455948048</t>
+          <t>https://m.place.naver.com/place/1604028285</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3348,29 +3352,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>뷰티써니</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ysp933@naver.com</t>
-        </is>
-      </c>
+          <t>뷰티좋은날 구미점</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1328-3062</t>
+          <t>0507-1329-8422</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 6 1층</t>
+          <t>경상북도 구미시 진평7길 29 뷰티좋은날</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysp933</t>
+          <t>https://www.instagram.com/a_good_day_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3405,13 +3405,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>511</v>
+        <v>1085</v>
       </c>
       <c r="Q32" t="n">
-        <v>182</v>
+        <v>44</v>
       </c>
       <c r="R32" t="n">
-        <v>693</v>
+        <v>1129</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3420,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1107699555</t>
+          <t>1358401448</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107699555</t>
+          <t>https://m.place.naver.com/place/1358401448</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3442,29 +3442,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>켈러네일</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>pgr8520@naver.com</t>
-        </is>
-      </c>
+          <t>르네일상스 뷰티</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>054-472-3512</t>
+          <t>0507-1321-3147</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로1길 7 골드클래스 상가 2층</t>
+          <t>경상북도 구미시 여헌로 63-1 1층 101호 르네일상스뷰티</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://instagram.com/keller_nail</t>
+          <t>https://www.instagram.com/re_nailssance/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3499,13 +3495,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="R33" t="n">
-        <v>327</v>
+        <v>224</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3510,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1996094770</t>
+          <t>1992506261</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1996094770</t>
+          <t>https://m.place.naver.com/place/1992506261</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3536,29 +3532,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>태닝하우스</t>
+          <t>이연지네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>skan564@naver.com</t>
+          <t>angel1989918@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>070-8100-6614</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로3길 18-1 3층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 3</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/skan564</t>
+          <t>http://www.instagram.com/leeyeonjinail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3573,7 +3565,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3593,13 +3585,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="Q34" t="n">
-        <v>279</v>
+        <v>93</v>
       </c>
       <c r="R34" t="n">
-        <v>304</v>
+        <v>195</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3608,17 +3600,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>36615392</t>
+          <t>21788268</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36615392</t>
+          <t>https://m.place.naver.com/place/21788268</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3630,34 +3622,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>당신의네일 구미점</t>
+          <t>네일그리다</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>moontique0812@naver.com</t>
+          <t>nailgreeda_@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1479-3375</t>
+          <t>0507-1344-0601</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동남길 114 1층</t>
+          <t>경상북도 구미시 옥계신당로5안길 14-2 103호 네일그리다</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Lo52PXzFyJ8</t>
+          <t>https://www.instagram.com/__nailgreeda</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3687,13 +3679,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>143</v>
+        <v>278</v>
       </c>
       <c r="Q35" t="n">
-        <v>153</v>
+        <v>13</v>
       </c>
       <c r="R35" t="n">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3702,17 +3694,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1917650763</t>
+          <t>1562146864</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1917650763</t>
+          <t>https://m.place.naver.com/place/1562146864</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3724,29 +3716,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>마인드민</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>bbang2ya_ho@naver.com</t>
-        </is>
-      </c>
+          <t>네일 클로버</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1349-3391</t>
+          <t>0507-1340-2851</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로 24 2층 213호</t>
+          <t>경상북도 구미시 인동36길 50 코리안빌 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mind.min__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3756,7 +3744,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3772,22 +3760,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3796,17 +3784,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1278996028</t>
+          <t>2042045182</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278996028</t>
+          <t>https://m.place.naver.com/place/2042045182</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3818,29 +3806,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일가연</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>shammy_1@naver.com</t>
-        </is>
-      </c>
+          <t>네일리 당신이 행복해지는 공간</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1347-7918</t>
+          <t>0507-1302-8151</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동15길 5 섬계빌딩 1층</t>
+          <t>경상북도 구미시 인동38길 15-14 101호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgayeon</t>
+          <t>https://instagram.com/nailee_gumi?utm_source=ig_profile_share&amp;igshid=1hfrq3xi83ko9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,7 +3850,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3875,13 +3859,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>261</v>
+        <v>172</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3890,17 +3874,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1868192073</t>
+          <t>1919352609</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868192073</t>
+          <t>https://m.place.naver.com/place/1919352609</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3912,29 +3896,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>문또네일</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>dmsrod91@naver.com</t>
-        </is>
-      </c>
+          <t>찐블링네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1411-4460</t>
+          <t>0507-1321-9103</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로1길 21-33 1층 문또네일</t>
+          <t>경상북도 구미시 인동중앙로7길 28 1층 106호 찐블링</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moontto_nail/</t>
+          <t>https://www.instagram.com/jjin_bling</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3969,13 +3949,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>231</v>
+        <v>38</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="R38" t="n">
-        <v>253</v>
+        <v>134</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3984,17 +3964,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1529598857</t>
+          <t>1435433966</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1529598857</t>
+          <t>https://m.place.naver.com/place/1435433966</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4006,29 +3986,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HAND</t>
+          <t>제이뷰티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wkosin@naver.com</t>
+          <t>j_beauty_9630@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1414-2054</t>
+          <t>0507-1457-9630</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로5길 35 1층</t>
+          <t>경상북도 구미시 산호대로33길 6-15 1층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3iH4qCh</t>
+          <t>http://pf.kakao.com/_HnwCX</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4063,13 +4043,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4078,17 +4058,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1782781735</t>
+          <t>1564361941</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782781735</t>
+          <t>https://m.place.naver.com/place/1564361941</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4100,29 +4080,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>홈네일</t>
+          <t>단아뷰티 네일바이진 산동점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>homenail_@naver.com</t>
+          <t>room11st@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>054-471-7708</t>
+          <t>0507-1344-7102</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동26길 54-1 1층</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 20 탑클래스빌딩 3층 305호 A</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/homenail_</t>
+          <t>https://blog.naver.com/room11st</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4157,13 +4137,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>299</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="R40" t="n">
-        <v>17</v>
+        <v>355</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4172,17 +4152,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>627597210</t>
+          <t>1224247985</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/627597210</t>
+          <t>https://m.place.naver.com/place/1224247985</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4194,34 +4174,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일,지야</t>
+          <t>네일도화</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kinshalouis@naver.com</t>
+          <t>khyun1029@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1355-4306</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동32길 40-1 1층 네일지야</t>
+          <t>경상북도 구미시 인동30길 23 1층 네일도화</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_ziya</t>
+          <t>http://pf.kakao.com/_sIxkjxj</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4242,7 +4218,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4251,13 +4227,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>188</v>
+        <v>53</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4266,17 +4242,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1337655355</t>
+          <t>1935081528</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1337655355</t>
+          <t>https://m.place.naver.com/place/1935081528</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4288,34 +4264,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>콩네일</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>lucia_1010@naver.com</t>
-        </is>
-      </c>
+          <t>네일은하</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0507-1395-8082</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경상북도 구미시 흥안로3길 11 1층</t>
+          <t>경상북도 구미시 여헌로7길 39-1 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cong_nail.jining1?igsh=MXJ6YXd4dXd0NGxybg==</t>
+          <t>http://pf.kakao.com/_xgFMxiG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4336,7 +4304,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4345,13 +4313,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4360,17 +4328,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2072633283</t>
+          <t>1541966803</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072633283</t>
+          <t>https://m.place.naver.com/place/1541966803</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4382,29 +4350,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>네일 희</t>
+          <t>주주모어네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nail-hee@naver.com</t>
+          <t>0636535529@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1304-0479</t>
+          <t>0507-1399-9336</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동15길 19 1층</t>
+          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤메디프라자2차 2층 202호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-hee</t>
+          <t>http://www.instagram.com/_juju_more</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4419,7 +4387,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4439,13 +4407,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="Q43" t="n">
-        <v>1226</v>
+        <v>73</v>
       </c>
       <c r="R43" t="n">
-        <v>1324</v>
+        <v>255</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4454,17 +4422,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1616482004</t>
+          <t>1091496299</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1616482004</t>
+          <t>https://m.place.naver.com/place/1091496299</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4476,29 +4444,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>르네일상스 뷰티</t>
+          <t>오로지푸스&amp;아르떼네일 구미옥계점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jy0_0640@naver.com</t>
+          <t>artenail0@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1321-3147</t>
+          <t>0507-1363-1778</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로 63-1 1층 101호 르네일상스뷰티</t>
+          <t>경상북도 구미시 산호대로31길 15 8층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_nailssance/</t>
+          <t>https://www.instagram.com/artenail_gumi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4533,13 +4501,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>1020</v>
       </c>
       <c r="R44" t="n">
-        <v>225</v>
+        <v>1070</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,17 +4516,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1992506261</t>
+          <t>37061075</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992506261</t>
+          <t>https://m.place.naver.com/place/37061075</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4570,30 +4538,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뷰티라움</t>
+          <t>나탈리네일 스튜디오</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>raum_chaeun@naver.com</t>
+          <t>soorokjip@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1328-9155</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 20 나동 6호</t>
+          <t>경상북도 칠곡군 석적읍 남율로9길 30 유진빌딩 1층 104호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/raum_chaeun</t>
+          <t>http://pf.kakao.com/_BhxaUT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4603,7 +4575,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4614,7 +4586,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4623,13 +4595,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>45</v>
+        <v>275</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>55</v>
+        <v>278</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4638,17 +4610,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1433414344</t>
+          <t>1011209011</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1433414344</t>
+          <t>https://m.place.naver.com/place/1011209011</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4660,29 +4632,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일온니</t>
+          <t>네일톡</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sunmoons2@naver.com</t>
+          <t>youming100@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1428-0388</t>
+          <t>0507-1360-5595</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 14 2층 지엘뷰티(네일온니)</t>
+          <t>경상북도 구미시 산호대로35길 17</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sunmoons2</t>
+          <t>https://www.instagram.com/nailtalk_jo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4697,7 +4669,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4717,13 +4689,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
+        <v>257</v>
       </c>
       <c r="R46" t="n">
-        <v>203</v>
+        <v>354</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,17 +4704,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1605125306</t>
+          <t>20734703</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1605125306</t>
+          <t>https://m.place.naver.com/place/20734703</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4754,25 +4726,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>오월에 네일</t>
+          <t>손톱모양</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1447-3385</t>
+          <t>0507-1468-8014</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 동중리3길 17 . 1층 오월에 네일</t>
+          <t>경상북도 구미시 산동읍 신당1로 58 다드림 5층 손톱모양</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/5may_nail</t>
+          <t>http://www.instagram.com/nail_moyang/</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4807,13 +4779,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4822,17 +4794,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1158180040</t>
+          <t>1534082815</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158180040</t>
+          <t>https://m.place.naver.com/place/1534082815</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4844,25 +4816,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>델라네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>네일바이진</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>room11st@naver.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1376-1778</t>
+          <t>0507-1362-8102</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로35길 18 1층 델라네일</t>
+          <t>경상북도 구미시 인동38길 9-4 구평종합프라자 D동 1층 108호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://instagram.com/della_nail_</t>
+          <t>http://instagram.com/nail__by__jin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4897,13 +4873,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>155</v>
+        <v>648</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="R48" t="n">
-        <v>172</v>
+        <v>736</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4912,17 +4888,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1036788315</t>
+          <t>252521148</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036788315</t>
+          <t>https://m.place.naver.com/place/252521148</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4934,34 +4910,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>봉봉네일</t>
+          <t>폭스네일</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ieeei13@naver.com</t>
+          <t>dksduwls1235@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1357-5294</t>
+          <t>0507-1366-2191</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리3길 67 2층</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_XEKRxb/chat</t>
+          <t>https://www.instagram.com/foxnail_85/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4982,7 +4958,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4991,13 +4967,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="Q49" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="R49" t="n">
-        <v>350</v>
+        <v>186</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5006,17 +4982,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>610087331</t>
+          <t>1356736986</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/610087331</t>
+          <t>https://m.place.naver.com/place/1356736986</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5004,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>이연지네일</t>
+          <t>홍샵네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -5037,12 +5013,12 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 3</t>
+          <t>경상북도 구미시 인동32길 14-5 천년나무 1층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/leeyeonjinail</t>
+          <t>https://www.instagram.com/_hongshop_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5068,7 +5044,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5077,13 +5053,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="Q50" t="n">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>195</v>
+        <v>42</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5092,17 +5068,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>21788268</t>
+          <t>1317894140</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21788268</t>
+          <t>https://m.place.naver.com/place/1317894140</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5114,34 +5090,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>제이뷰티</t>
+          <t>뷰티써니</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>j_beauty_9630@naver.com</t>
+          <t>ysp933@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1457-9630</t>
+          <t>0507-1328-3062</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로33길 6-15 1층</t>
+          <t>경상북도 구미시 여헌로 6 1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HnwCX</t>
+          <t>https://blog.naver.com/ysp933</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5151,7 +5127,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5162,7 +5138,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5171,13 +5147,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>97</v>
+        <v>511</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="R51" t="n">
-        <v>109</v>
+        <v>693</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5186,17 +5162,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1564361941</t>
+          <t>1107699555</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564361941</t>
+          <t>https://m.place.naver.com/place/1107699555</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5208,26 +5184,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>디오르 네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>네일코드</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bongbong323@naver.com</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1479-7046</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동20길 27-36 1층 디오르네일</t>
+          <t>경상북도 구미시 산동읍 신당인덕1로1길 24 1층, 네일코드</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/DIORENAIL</t>
+          <t>http://pf.kakao.com/_xlixbin/chat</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5248,7 +5232,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5257,13 +5241,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5272,17 +5256,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1105211647</t>
+          <t>1691163537</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1105211647</t>
+          <t>https://m.place.naver.com/place/1691163537</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5294,30 +5278,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>별처럼 빛나는</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>네일룸</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gumi_nailroom@naver.com</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1339-8609</t>
+          <t>0507-1415-4865</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동46길 37-11 1층 별처럼 빛나는</t>
+          <t>경상북도 구미시 인동가산로 14 메가박스 4층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/starlight.nail_</t>
+          <t>https://blog.naver.com/gumi_nailroom</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5347,13 +5335,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>320</v>
+        <v>128</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R53" t="n">
-        <v>335</v>
+        <v>140</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5362,17 +5350,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1789448790</t>
+          <t>120181172</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1789448790</t>
+          <t>https://m.place.naver.com/place/120181172</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5384,25 +5372,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일은하</t>
+          <t>HAND</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>lucia_1010@naver.com</t>
+          <t>wkosin@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1414-2054</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경상북도 구미시 여헌로7길 39-1 1층</t>
+          <t>경상북도 구미시 옥계신당로5길 35 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xgFMxiG</t>
+          <t>https://open.kakao.com/o/s3iH4qCh</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5437,13 +5429,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R54" t="n">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5452,17 +5444,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1541966803</t>
+          <t>1782781735</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1541966803</t>
+          <t>https://m.place.naver.com/place/1782781735</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5474,34 +5466,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일바이진</t>
+          <t>로오브 네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>room11st@naver.com</t>
+          <t>uiouio_0@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1362-8102</t>
+          <t>0507-1363-9321</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 9-4 구평종합프라자 D동 1층 108호</t>
+          <t>경상북도 구미시 옥계신당로5길 25-19 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail__by__jin</t>
+          <t>http://pf.kakao.com/_xoUglG</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5522,7 +5514,7 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5531,13 +5523,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>648</v>
+        <v>150</v>
       </c>
       <c r="Q55" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="R55" t="n">
-        <v>736</v>
+        <v>210</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5546,17 +5538,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>252521148</t>
+          <t>1760682520</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/252521148</t>
+          <t>https://m.place.naver.com/place/1760682520</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5568,21 +5560,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ahoi Room[아효이룸]</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>벨네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>aa8852@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1375-2916</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로5길 16-11 1층 ahoi room 아효이룸</t>
+          <t>경상북도 구미시 여헌로 38-10 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xeABmn</t>
+          <t>https://m.place.naver.com/place/1947942533/home?entry=pll</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5617,13 +5617,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>407</v>
+        <v>128</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5632,17 +5632,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>37322848</t>
+          <t>1214410327</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37322848</t>
+          <t>https://m.place.naver.com/place/1214410327</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5654,29 +5654,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>뮤네일</t>
+          <t>뷰티라움</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mieux_by_nail@naver.com</t>
+          <t>raum_chaeun@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1345-1605</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로1길 15 골드클래스 상가</t>
+          <t>경상북도 칠곡군 석적읍 유학로 20 나동 6호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://instagram.com/_mew_nail</t>
+          <t>https://blog.naver.com/raum_chaeun</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5691,7 +5687,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5711,13 +5707,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R57" t="n">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5726,17 +5722,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1948081087</t>
+          <t>1433414344</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948081087</t>
+          <t>https://m.place.naver.com/place/1433414344</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5748,34 +5744,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일드인</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>m__hinail@naver.com</t>
-        </is>
-      </c>
+          <t>네일을그리다</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1364-2315</t>
+          <t>0507-1483-1005</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로3길 6 네일드인</t>
+          <t>경상북도 구미시 인동11길 16-5 1층 네일을그리다</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xduSGG</t>
+          <t>https://www.instagram.com/nail.__.grida</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5796,7 +5788,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5805,13 +5797,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1490</v>
+        <v>167</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>1493</v>
+        <v>169</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5820,17 +5812,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1922958194</t>
+          <t>1194330297</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1922958194</t>
+          <t>https://m.place.naver.com/place/1194330297</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5842,29 +5834,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>마리네일</t>
+          <t>네일온니</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>hydestocker@naver.com</t>
+          <t>sunmoons2@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1417-1570</t>
+          <t>0507-1428-0388</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동북길 175 1층</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 14 2층 지엘뷰티(네일온니)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/marinail__gumi__</t>
+          <t>https://blog.naver.com/sunmoons2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5879,7 +5871,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5899,13 +5891,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="Q59" t="n">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="R59" t="n">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5914,17 +5906,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>178032643</t>
+          <t>1605125306</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/178032643</t>
+          <t>https://m.place.naver.com/place/1605125306</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5936,25 +5928,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일공간</t>
+          <t>문또네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>winkyster@naver.com</t>
+          <t>dmsrod91@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1411-4460</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로1길 2-1 1층 NAIL공간</t>
+          <t>경상북도 구미시 옥계신당로1길 21-33 1층 문또네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.gonggan_</t>
+          <t>https://www.instagram.com/moontto_nail/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5989,13 +5985,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R60" t="n">
-        <v>141</v>
+        <v>254</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6004,17 +6000,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1284979937</t>
+          <t>1529598857</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284979937</t>
+          <t>https://m.place.naver.com/place/1529598857</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6026,29 +6022,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>손끝네일</t>
+          <t>꼼꼼네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>pp1102qq@naver.com</t>
+          <t>papa_ma@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1427-6878</t>
+          <t>0507-1323-9839</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동19길 27-4 다옴빌 1층</t>
+          <t>경상북도 칠곡군 석적읍 서중리6길 38</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pp1102qq</t>
+          <t>http://instagram.com/_kkomkkom_nail</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6063,7 +6059,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6083,13 +6079,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>65</v>
+        <v>474</v>
       </c>
       <c r="Q61" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="R61" t="n">
-        <v>86</v>
+        <v>500</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6098,17 +6094,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>952100686</t>
+          <t>36630885</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/952100686</t>
+          <t>https://m.place.naver.com/place/36630885</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6120,25 +6116,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>뷰티플럼</t>
+          <t>네일 빛나</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>heysoo206@naver.com</t>
+          <t>jewell1004@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1417-0501</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 15 1층</t>
+          <t>경상북도 구미시 옥계북로10길 3-30 아트빌 1층 네일빛나</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty__plum</t>
+          <t>https://www.instagram.com/nail._.bitna</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6164,7 +6164,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6173,13 +6173,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6188,17 +6188,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1498423201</t>
+          <t>1324129585</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498423201</t>
+          <t>https://m.place.naver.com/place/1324129585</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6210,29 +6210,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>하이비뷰티&amp;풋 본점</t>
+          <t>별처럼 빛나는</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>tree4350@naver.com</t>
+          <t>bright_as_stars@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1385-7396</t>
+          <t>0507-1339-8609</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 72 하이비뷰티&amp;풋 본점</t>
+          <t>경상북도 구미시 인동46길 37-11 1층 별처럼 빛나는</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sj_hib.beauty/</t>
+          <t>https://www.instagram.com/starlight.nail_</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="Q63" t="n">
-        <v>1138</v>
+        <v>15</v>
       </c>
       <c r="R63" t="n">
-        <v>1484</v>
+        <v>336</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6282,17 +6282,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1877586341</t>
+          <t>1789448790</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877586341</t>
+          <t>https://m.place.naver.com/place/1789448790</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6304,25 +6304,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일을그리다</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>이현네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>tt68252@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1483-1005</t>
+          <t>0507-1477-7997</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동11길 16-5 1층 네일을그리다</t>
+          <t>경상북도 구미시 인동19길 34 1층 103호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.__.grida</t>
+          <t>https://www.instagram.com/leehyun_studio</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6357,13 +6361,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>167</v>
+        <v>18</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="R64" t="n">
-        <v>169</v>
+        <v>318</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6372,17 +6376,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1194330297</t>
+          <t>1200581636</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194330297</t>
+          <t>https://m.place.naver.com/place/1200581636</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6394,29 +6398,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>뷰티첼리</t>
+          <t>네일,지야</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>wlsl604@naver.com</t>
+          <t>kinshalouis@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1356-0944</t>
+          <t>0507-1355-4306</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 22 타워밸리 1동 2층 201호, 202호</t>
+          <t>경상북도 구미시 인동32길 40-1 1층 네일지야</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beautycelli_nail/</t>
+          <t>https://www.instagram.com/nail_ziya</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6451,13 +6455,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>709</v>
+        <v>187</v>
       </c>
       <c r="Q65" t="n">
-        <v>706</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>1415</v>
+        <v>188</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6466,17 +6470,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>31143856</t>
+          <t>1337655355</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31143856</t>
+          <t>https://m.place.naver.com/place/1337655355</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6488,21 +6492,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>도디네일</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>켈러네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pgr8520@naver.com</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>054-472-3512</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동28길 57-7 그리네빌 1층</t>
+          <t>경상북도 구미시 산동읍 신당2로1길 7 골드클래스 상가 2층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dodi._.nail</t>
+          <t>http://instagram.com/keller_nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6537,13 +6549,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>28</v>
+        <v>284</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="R66" t="n">
-        <v>29</v>
+        <v>327</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6552,17 +6564,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1754437228</t>
+          <t>1996094770</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1754437228</t>
+          <t>https://m.place.naver.com/place/1996094770</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6574,29 +6586,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>찐블링네일</t>
+          <t>콩네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hwhoskyj59@naver.com</t>
+          <t>ttltjsdla@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1321-9103</t>
+          <t>0507-1395-8082</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로7길 28 1층 106호 찐블링</t>
+          <t>경상북도 구미시 흥안로3길 11 1층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jjin_bling</t>
+          <t>https://www.instagram.com/cong_nail.jining1?igsh=MXJ6YXd4dXd0NGxybg==</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6631,13 +6643,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="Q67" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6646,17 +6658,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1435433966</t>
+          <t>2072633283</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435433966</t>
+          <t>https://m.place.naver.com/place/2072633283</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6668,29 +6680,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일리유</t>
+          <t>오랑쥬네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>lhll0228@naver.com</t>
+          <t>naribaba@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1448-1142</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동30길 4 1층</t>
+          <t>경상북도 구미시 인동36길 17 보람빌딩 5층 라지공유오피스 6호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/naily__u</t>
+          <t>https://www.instagram.com/org_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6725,13 +6733,13 @@
         </is>
       </c>
       <c r="P68" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q68" t="n">
         <v>2</v>
       </c>
-      <c r="Q68" t="n">
-        <v>25</v>
-      </c>
       <c r="R68" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6740,17 +6748,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1604028285</t>
+          <t>2094064094</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1604028285</t>
+          <t>https://m.place.naver.com/place/2094064094</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6762,34 +6770,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>주주모어네일</t>
+          <t>봉봉네일</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6qbmfuw6c@naver.com</t>
+          <t>ieeei13@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1399-9336</t>
+          <t>0507-1357-5294</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤메디프라자2차 2층 202호</t>
+          <t>경상북도 칠곡군 석적읍 북중리3길 67 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_juju_more</t>
+          <t>http://pf.kakao.com/_XEKRxb/chat</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6810,7 +6818,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6819,13 +6827,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>182</v>
+        <v>283</v>
       </c>
       <c r="Q69" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="R69" t="n">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6834,17 +6842,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1091496299</t>
+          <t>610087331</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091496299</t>
+          <t>https://m.place.naver.com/place/610087331</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6856,29 +6864,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일모노</t>
+          <t>레푸스 구미산동점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ekgus9633@naver.com</t>
+          <t>onyoubang@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1484-2855</t>
+          <t>0507-1442-4774</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계신당로1길 1-15 1층</t>
+          <t>경상북도 구미시 산동읍 신당1로1길 17-7 2층 208호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.mono_?igsh=MTQ1M2I3ajJma3M2dA==</t>
+          <t>http://instagram.com/refuss_sandong</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6913,13 +6921,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R70" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6928,17 +6936,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>2055274089</t>
+          <t>1150432914</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055274089</t>
+          <t>https://m.place.naver.com/place/1150432914</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6950,34 +6958,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>나탈리네일 스튜디오</t>
+          <t>네일있지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>frenchcloset@naver.com</t>
+          <t>gold77com@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1328-9155</t>
+          <t>0507-1391-1297</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 남율로9길 30 유진빌딩 1층 104호</t>
+          <t>경상북도 구미시 산동읍 신당1로3길 19 6층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_BhxaUT</t>
+          <t>https://www.instagram.com/nail_itzy</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6998,7 +7006,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7007,13 +7015,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R71" t="n">
-        <v>276</v>
+        <v>26</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7022,17 +7030,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1011209011</t>
+          <t>1679291687</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011209011</t>
+          <t>https://m.place.naver.com/place/1679291687</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7044,12 +7052,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일연구소</t>
+          <t>나비드뷰티</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jyedream@naver.com</t>
+          <t>xoghks425588@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7057,22 +7065,22 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동54안길 6-19 1층</t>
+          <t>경상북도 구미시 산동읍 신당인덕2로2길 4-9 103호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xlxhpVs</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7088,22 +7096,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R72" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7112,17 +7120,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1916131367</t>
+          <t>1006406463</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1916131367</t>
+          <t>https://m.place.naver.com/place/1006406463</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7134,34 +7142,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오로지푸스&amp;아르떼네일 구미옥계점</t>
+          <t>당신의네일 구미점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>artenail0@naver.com</t>
+          <t>moontique0812@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1363-1778</t>
+          <t>0507-1479-3375</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로31길 15 8층</t>
+          <t>경상북도 구미시 인동남길 114 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artenail_gumi</t>
+          <t>https://youtube.com/watch?v=Lo52PXzFyJ8</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7191,13 +7199,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="Q73" t="n">
-        <v>1020</v>
+        <v>153</v>
       </c>
       <c r="R73" t="n">
-        <v>1070</v>
+        <v>296</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7206,17 +7214,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>37061075</t>
+          <t>1917650763</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37061075</t>
+          <t>https://m.place.naver.com/place/1917650763</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7228,29 +7236,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>폭스네일</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>kde529@naver.com</t>
-        </is>
-      </c>
+          <t>섬섬네일 석적본점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1366-2191</t>
+          <t>0507-1356-4712</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로3길 19</t>
+          <t>경상북도 칠곡군 석적읍 서중리6길 44 1층 102호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/foxnail_85/</t>
+          <t>https://www.instagram.com/somseom._.nail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7285,13 +7289,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7300,17 +7304,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1356736986</t>
+          <t>1767641632</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356736986</t>
+          <t>https://m.place.naver.com/place/1767641632</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7322,29 +7326,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이현네일스튜디오</t>
+          <t>남자다운네일 구평점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>tt68252@naver.com</t>
+          <t>dbs0896@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1477-7997</t>
+          <t>054-471-7396</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동19길 34 1층 103호</t>
+          <t>경상북도 구미시 인동38길 15-6 금강빌딩 103호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leehyun_studio</t>
+          <t>https://blog.naver.com/dbs0896</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7359,7 +7363,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7379,13 +7383,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="n">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="R75" t="n">
-        <v>318</v>
+        <v>35</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7394,17 +7398,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1200581636</t>
+          <t>34362850</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200581636</t>
+          <t>https://m.place.naver.com/place/34362850</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7416,29 +7420,21 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>네일우디</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>90heehee@naver.com</t>
-        </is>
-      </c>
+          <t>네일연구소</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1303-5277</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 동서6길 28-14 2층 202호</t>
+          <t>경상북도 구미시 인동54안길 6-19 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailwoody_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7448,7 +7444,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7469,17 +7465,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7488,17 +7484,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1969430230</t>
+          <t>1916131367</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1969430230</t>
+          <t>https://m.place.naver.com/place/1916131367</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
